--- a/ZáróProjekt/zaroprojekt.xlsx
+++ b/ZáróProjekt/zaroprojekt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\Diákoknak\Dávid Márta\12.G\ZáróProjekt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16BB1F25-3390-437C-BE72-0DE47C7E20E0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD074D52-516F-46D4-B497-4D77F7706C4F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -317,13 +317,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -643,7 +643,7 @@
       <c r="D3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="19">
         <v>2</v>
       </c>
     </row>
@@ -660,7 +660,7 @@
       <c r="D4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="19">
+      <c r="E4" s="20">
         <v>1</v>
       </c>
     </row>
@@ -677,7 +677,7 @@
       <c r="D5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="20">
         <v>4</v>
       </c>
     </row>
@@ -692,7 +692,7 @@
       <c r="D6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="20">
         <v>3</v>
       </c>
     </row>
@@ -707,7 +707,7 @@
       <c r="D7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="20">
         <v>8</v>
       </c>
     </row>
@@ -724,7 +724,7 @@
       <c r="D8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="20">
         <v>7</v>
       </c>
     </row>
@@ -739,7 +739,7 @@
       <c r="D9" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="19">
+      <c r="E9" s="20">
         <v>5</v>
       </c>
     </row>
@@ -752,7 +752,7 @@
         <v>19</v>
       </c>
       <c r="D10" s="7"/>
-      <c r="E10" s="20">
+      <c r="E10" s="21">
         <v>6</v>
       </c>
     </row>
